--- a/docs/observable/kv-client-excel/kv-client-观测-调用链与URMA-TCP.xlsx
+++ b/docs/observable/kv-client-excel/kv-client-观测-调用链与URMA-TCP.xlsx
@@ -517,8 +517,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>K_INVALID
-- K_INVALID: 入参非法（如 key/offset/timeout/batch 越界）</t>
+          <t>- K_INVALID: 入参非法（如 key/offset/timeout/batch 越界）</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -552,7 +551,8 @@
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>返回: 直接RETURN；重试: 通常不重试。
-- 代码锚点: object_client_impl.cpp Init</t>
+- 代码锚点: object_client_impl.cpp Init
+- 代码证据: object_client_impl.cpp:297 296:{ | 297:CHECK_FAIL_RETURN_STATUS(connectTimeoutMs_ &gt;= 0, K_INVALID, "The connection timeout must be a positive integer."); | 298:HeartbeatType heartbeatType = enableHeartbeat ? HeartbeatType::RPC_HEARTBEAT : HeartbeatType::NO_HEARTBEAT;</t>
         </is>
       </c>
     </row>
@@ -580,8 +580,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>1002/1001; Register client failed
-- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
+          <t>- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
 - K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用</t>
         </is>
       </c>
@@ -624,7 +623,8 @@
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>返回: Status返回；重试: 通常不重试。
-- 代码锚点: client_worker_common_api.cpp Connect</t>
+- 代码锚点: client_worker_common_api.cpp Connect
+- 代码证据: client_worker_common_api.cpp:191 190:Status status; | 191:RETURN_IF_NOT_OK_PRINT_ERROR_MSG(api_-&gt;WorkerRegisterClient(workerService_, req, rsp), "Register client failed"); | 192:VLOG(1) &lt;&lt; "Register response: " &lt;&lt; rsp.DebugString();</t>
         </is>
       </c>
     </row>
@@ -652,8 +652,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1002/1001/19; timeout/unavailable/try_again
-- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
+          <t>- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
 - K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用
 - K_TRY_AGAIN(19): 瞬时错误，建议按策略重试</t>
         </is>
@@ -698,7 +697,8 @@
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>返回: 状态直接返回；重试: 连接阶段通常快速失败，业务RPC阶段按 RetryOnError 对 1001/1002/19 退避重试。
-- 代码锚点: client_worker_common_api.cpp; client_worker_remote_api.cpp</t>
+- 代码锚点: client_worker_common_api.cpp; client_worker_remote_api.cpp
+- 代码证据: client_worker_common_api.cpp:136 136:RETURN_STATUS(K_RUNTIME_ERROR, "Not support GetClientFd in embedded scenario");</t>
         </is>
       </c>
     </row>
@@ -720,13 +720,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>UMDK/URMA</t>
+          <t>URMA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1004; Failed to urma init
-- K_URMA_ERROR(1004): URMA调用失败（初始化/队列/数据面）</t>
+          <t>- K_URMA_ERROR(1004): URMA调用失败（初始化/队列/数据面）</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -767,7 +766,8 @@
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>返回: LOG_IF_ERROR不阻断Init；重试: 通常不重试。
-- 代码锚点: urma_manager.cpp UrmaInit</t>
+- 代码锚点: urma_manager.cpp UrmaInit
+- 代码证据: urma_manager.cpp:270 269:if (ret != URMA_SUCCESS) { | 270:RETURN_STATUS_LOG_ERROR(K_URMA_ERROR, FormatString("Failed to urma init, ret = %d", ret)); | 271:}</t>
         </is>
       </c>
     </row>
@@ -793,8 +793,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>K_OUT_OF_MEMORY(6); Failed to allocate memory buffer pool
-- K_OUT_OF_MEMORY(6): 内存不足（UB池/请求处理过程）</t>
+          <t>- K_OUT_OF_MEMORY(6): 内存不足（UB池/请求处理过程）</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -835,7 +834,8 @@
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>返回: 链上RETURN；重试: 通常不重试。
-- 代码锚点: urma_manager.cpp InitMemoryBufferPool</t>
+- 代码锚点: urma_manager.cpp InitMemoryBufferPool
+- 代码证据: urma_manager.cpp:201 200:if (memoryBuffer_ == nullptr) { | 201:RETURN_STATUS(K_OUT_OF_MEMORY, "Failed to allocate memory buffer pool for client"); | 202:}</t>
         </is>
       </c>
     </row>
@@ -857,13 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>UMDK/URMA</t>
+          <t>URMA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Fast transport handshake failed…fall back
-- （无明确内部枚举）: 当前case以系统侧日志/状态为主，请结合Sheet2/3定位</t>
+          <t>- （无明确内部枚举）: 当前case以系统侧日志/状态为主，请结合Sheet2/3定位</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -903,7 +902,8 @@
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>返回: 仅ERROR日志；重试: 通常不重试。
-- 代码锚点: urma_manager.cpp ExchangeJfr</t>
+- 代码锚点: urma_manager.cpp ExchangeJfr
+- 代码证据: urma_manager.cpp:63 63:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
         </is>
       </c>
     </row>
@@ -930,8 +930,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>K_UNKNOWN_ERROR; Pass fd…/invalid fd
-- K_UNKNOWN_ERROR: 未知错误（常见于fd传递异常等）</t>
+          <t>- K_UNKNOWN_ERROR: 未知错误（常见于fd传递异常等）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -973,7 +972,8 @@
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>返回: 线程内失败；重试: 通常不重试。
-- 代码锚点: fd_pass.cpp SockRecvFd</t>
+- 代码锚点: fd_pass.cpp SockRecvFd
+- 代码证据: fd_pass.cpp:49 49:CHECK_FAIL_RETURN_STATUS(ret == EOK, StatusCode::K_RUNTIME_ERROR,</t>
         </is>
       </c>
     </row>
@@ -1001,8 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>K_INVALID; subTimeoutMs out of range
-- K_INVALID: 入参非法（如 key/offset/timeout/batch 越界）
+          <t>- K_INVALID: 入参非法（如 key/offset/timeout/batch 越界）
 - K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢</t>
         </is>
       </c>
@@ -1037,7 +1036,8 @@
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>返回: 直接RETURN；重试: 通常不重试。
-- 代码锚点: client_worker_base_api.cpp PreGet</t>
+- 代码锚点: client_worker_base_api.cpp PreGet
+- 代码证据: client_worker_base_api.cpp:39 39:LOG(INFO) &lt;&lt; FormatString("Begin to publish object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -1058,13 +1058,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UMDK/URMA</t>
+          <t>URMA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>WARNING; fallback to TCP/IP payload
-- （无明确内部枚举）: 当前case以系统侧日志/状态为主，请结合Sheet2/3定位</t>
+          <t>- （无明确内部枚举）: 当前case以系统侧日志/状态为主，请结合Sheet2/3定位</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1104,7 +1103,8 @@
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>返回: 不返回URMA码继续RPC；重试: 通常不重试。
-- 代码锚点: client_worker_base_api.cpp PrepareUrmaBuffer</t>
+- 代码锚点: client_worker_base_api.cpp PrepareUrmaBuffer
+- 代码证据: client_worker_base_api.cpp:82 81:if (ubRc.IsError()) { | 82:LOG(WARNING) &lt;&lt; "Prepare UB Get request failed: " &lt;&lt; ubRc.ToString() &lt;&lt; ", fallback to TCP/IP payload."; | 83:ubBufferHandle.reset();</t>
         </is>
       </c>
     </row>
@@ -1131,8 +1131,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1001/1002/19; RPC Retry detail
-- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
+          <t>- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
 - K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用
 - K_TRY_AGAIN(19): 瞬时错误，建议按策略重试</t>
         </is>
@@ -1176,7 +1175,8 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>返回: Status返回；重试: RetryOnError。
-- 代码锚点: client_worker_remote_api.cpp Get</t>
+- 代码锚点: client_worker_remote_api.cpp Get
+- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -1203,8 +1203,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1001/1002/19; timeout/unavailable/try_again
-- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
+          <t>- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
 - K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用
 - K_TRY_AGAIN(19): 瞬时错误，建议按策略重试</t>
         </is>
@@ -1249,7 +1248,8 @@
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>返回: 重试后返回；重试: RetryOnError。
-- 代码锚点: client_worker_remote_api.cpp</t>
+- 代码锚点: client_worker_remote_api.cpp
+- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -1276,8 +1276,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>last_rc 1001/19/6+全失败
-- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
+          <t>- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
 - K_TRY_AGAIN(19): 瞬时错误，建议按策略重试
 - K_OUT_OF_MEMORY(6): 内存不足（UB池/请求处理过程）</t>
         </is>
@@ -1321,7 +1320,8 @@
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>返回: 重试；重试: 见RPC。
-- 代码锚点: client_worker_remote_api.cpp Get lambda</t>
+- 代码锚点: client_worker_remote_api.cpp Get lambda
+- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -1347,8 +1347,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1002; etcd is unavailable
-- K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用</t>
+          <t>- K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1390,7 +1389,8 @@
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>返回: last_rc；重试: worker内策略。
-- 代码锚点: worker_oc_service_get_impl.cpp</t>
+- 代码锚点: worker_oc_service_get_impl.cpp
+- 代码证据: worker_oc_service_get_impl.cpp:1583 1582:auto metaPb = std::make_unique&lt;ObjectMetaPb&gt;(); | 1583:CHECK_FAIL_RETURN_STATUS(!etcdStore_-&gt;IsKeepAliveTimeout(), K_RPC_UNAVAILABLE, "etcd is unavailable"); | 1584:RangeSearchResult res;</t>
         </is>
       </c>
     </row>
@@ -1411,13 +1411,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RPC框架</t>
+          <t>数据系统</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>K_RUNTIME_ERROR; Query from master failed
-- K_RUNTIME_ERROR(5): 运行时错误（如payload组装、mmap链路、URMA读写失败）</t>
+          <t>- K_RUNTIME_ERROR(5): 运行时错误（如payload组装、mmap链路、URMA读写失败）</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1451,7 +1450,8 @@
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>返回: last_rc；重试: 视实现。
-- 代码锚点: worker_oc_service_get_impl.cpp</t>
+- 代码锚点: worker_oc_service_get_impl.cpp
+- 代码证据: worker_oc_service_get_impl.cpp:700 699:} | 700:RETURN_STATUS_LOG_ERROR(K_RUNTIME_ERROR, FormatString("Query from master failed : %s", result.ToString())); | 701:}</t>
         </is>
       </c>
     </row>
@@ -1472,13 +1472,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RPC框架</t>
+          <t>数据系统</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Get from remote failed; 1002
-- K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用</t>
+          <t>- K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1520,7 +1519,8 @@
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>返回: last_rc/RPC；重试: TryReconnect…。
-- 代码锚点: worker_oc_service_get_impl.cpp</t>
+- 代码锚点: worker_oc_service_get_impl.cpp
+- 代码证据: worker_oc_service_get_impl.cpp:1733 1732:} else { | 1733:LOG(ERROR) &lt;&lt; FormatString("[ObjectKey %s] Get from remote failed: %s.", objectKey, status.ToString()); | 1734:failedIds.emplace(objectKey);</t>
         </is>
       </c>
     </row>
@@ -1541,13 +1541,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>UMDK/URMA</t>
+          <t>URMA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>K_RUNTIME_ERROR; Failed to urma write/read
-- K_RUNTIME_ERROR(5): 运行时错误（如payload组装、mmap链路、URMA读写失败）</t>
+          <t>- K_RUNTIME_ERROR(5): 运行时错误（如payload组装、mmap链路、URMA读写失败）</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1587,7 +1586,8 @@
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>返回: 汇总回 client；重试: 通常不重试。
-- 代码锚点: urma_manager.cpp</t>
+- 代码锚点: urma_manager.cpp
+- 代码证据: urma_manager.cpp:63 63:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
         </is>
       </c>
     </row>
@@ -1608,13 +1608,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>UMDK/URMA</t>
+          <t>URMA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1004; Failed to poll/wait jfc
-- K_URMA_ERROR(1004): URMA调用失败（初始化/队列/数据面）</t>
+          <t>- K_URMA_ERROR(1004): URMA调用失败（初始化/队列/数据面）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1663,7 +1662,8 @@
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>返回: 汇总回 client；重试: 通常不重试。
-- 代码锚点: urma_manager.cpp PollJfcWait</t>
+- 代码锚点: urma_manager.cpp PollJfcWait
+- 代码证据: urma_manager.cpp:63 63:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
         </is>
       </c>
     </row>
@@ -1683,13 +1683,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UMDK/URMA</t>
+          <t>URMA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1006; need to reconnect
-- K_URMA_NEED_CONNECT(1006): URMA连接不稳定或已断开，需要重连</t>
+          <t>- K_URMA_NEED_CONNECT(1006): URMA连接不稳定或已断开，需要重连</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1728,7 +1727,8 @@
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>返回: Status；重试: 通常不重试。
-- 代码锚点: urma_manager.cpp</t>
+- 代码锚点: urma_manager.cpp
+- 代码证据: urma_manager.cpp:1263 1262:} | 1263:RETURN_STATUS(K_URMA_NEED_CONNECT, "Urma connect unstable, need to reconnect!"); | 1264:}</t>
         </is>
       </c>
     </row>
@@ -1749,13 +1749,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UMDK/URMA</t>
+          <t>URMA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>K_RUNTIME_ERROR(5); UB payload overflow
-- K_RUNTIME_ERROR(5): 运行时错误（如payload组装、mmap链路、URMA读写失败）</t>
+          <t>- K_RUNTIME_ERROR(5): 运行时错误（如payload组装、mmap链路、URMA读写失败）</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1789,7 +1788,8 @@
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>返回: 直接RETURN；重试: 通常不重试。
-- 代码锚点: client_worker_base_api.cpp FillUrmaBuffer</t>
+- 代码锚点: client_worker_base_api.cpp FillUrmaBuffer
+- 代码证据: client_worker_base_api.cpp:107 106:ubReadOffset &lt;= ubBufferSize &amp;&amp; payloadSize &lt;= ubBufferSize - ubReadOffset, K_RUNTIME_ERROR, | 107:FormatString("UB payload overflow, object %s, payload size %llu, consumed %llu, buffer size %llu", | 108:payloadInfo-&gt;object_key(), payloadSize, ubReadOffset, ubBufferSize));</t>
         </is>
       </c>
     </row>
@@ -1815,8 +1815,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Get mmap entry failed
-- （无明确内部枚举）: 当前case以系统侧日志/状态为主，请结合Sheet2/3定位</t>
+          <t>- （无明确内部枚举）: 当前case以系统侧日志/状态为主，请结合Sheet2/3定位</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1857,7 +1856,8 @@
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>返回: 单key失败聚合；重试: 通常不重试。
-- 代码锚点: object_client_impl.cpp MmapShmUnit</t>
+- 代码锚点: object_client_impl.cpp MmapShmUnit
+- 代码证据: object_client_impl.cpp:1112 1111:mmapEntry = mmapManager_-&gt;GetMmapEntryByFd(shmBuf-&gt;fd); | 1112:CHECK_FAIL_RETURN_STATUS(mmapEntry != nullptr, StatusCode::K_RUNTIME_ERROR, "Get mmap entry failed"); | 1113:bufferInfo =</t>
         </is>
       </c>
     </row>
@@ -1882,8 +1882,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>K_NOT_FOUND
-- K_NOT_FOUND: 对象不存在或已过期</t>
+          <t>- K_NOT_FOUND: 对象不存在或已过期</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1917,7 +1916,8 @@
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>返回: last_rc；重试: 通常不重试。
-- 代码锚点: worker_oc_service_get_impl.cpp</t>
+- 代码锚点: worker_oc_service_get_impl.cpp
+- 代码证据: worker_oc_service_get_impl.cpp:250 249:(void)RemoveLocation(objectKey, version); | 250:return Status(StatusCode::K_NOT_FOUND, "Object not found"); | 251:}</t>
         </is>
       </c>
     </row>
@@ -1938,13 +1938,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>UMDK/URMA</t>
+          <t>URMA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>K_INVALID; Failed to send buffer via UB
-- K_INVALID: 入参非法（如 key/offset/timeout/batch 越界）</t>
+          <t>- K_INVALID: 入参非法（如 key/offset/timeout/batch 越界）</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1984,7 +1983,8 @@
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>返回: 可改走非UB；重试: 通常不重试。
-- 代码锚点: client_worker_base_api.cpp SendBufferViaUb</t>
+- 代码锚点: client_worker_base_api.cpp SendBufferViaUb
+- 代码证据: client_worker_base_api.cpp:146 145:#endif | 146:return Status(K_INVALID, "Failed to send buffer via UB"); | 147:}</t>
         </is>
       </c>
     </row>
@@ -2011,8 +2011,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1001/1002/19
-- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
+          <t>- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
 - K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用
 - K_TRY_AGAIN(19): 瞬时错误，建议按策略重试</t>
         </is>
@@ -2056,7 +2055,8 @@
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>返回: Status；重试: RetryOnError。
-- 代码锚点: client_worker_remote_api.cpp Publish</t>
+- 代码锚点: client_worker_remote_api.cpp Publish
+- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -2082,8 +2082,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1001/1002/19
-- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
+          <t>- K_RPC_DEADLINE_EXCEEDED(1001): RPC超时，通常为网络抖动/队列等待/对端慢
 - K_RPC_UNAVAILABLE(1002): RPC不可达，常见于连接失败或对端不可用
 - K_TRY_AGAIN(19): 瞬时错误，建议按策略重试</t>
         </is>
@@ -2128,7 +2127,8 @@
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>返回: 重试后返回；重试: RetryOnError。
-- 代码锚点: client_worker_remote_api.cpp</t>
+- 代码锚点: client_worker_remote_api.cpp
+- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -2154,8 +2154,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>32 K_SCALING; 6 OOM
-- K_OUT_OF_MEMORY(6): 内存不足（UB池/请求处理过程）
+          <t>- K_OUT_OF_MEMORY(6): 内存不足（UB池/请求处理过程）
 - K_SCALING(32): 集群扩缩容窗口触发的暂时性错误</t>
         </is>
       </c>
@@ -2190,7 +2189,8 @@
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>返回: Status；重试: RetryOnError含扩展码。
-- 代码锚点: client_worker_remote_api.cpp MultiPublish</t>
+- 代码锚点: client_worker_remote_api.cpp MultiPublish
+- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>

--- a/docs/observable/kv-client-excel/kv-client-观测-调用链与URMA-TCP.xlsx
+++ b/docs/observable/kv-client-excel/kv-client-观测-调用链与URMA-TCP.xlsx
@@ -552,7 +552,7 @@
         <is>
           <t>返回: 直接RETURN；重试: 通常不重试。
 - 代码锚点: object_client_impl.cpp Init
-- 代码证据: object_client_impl.cpp:297 296:{ | 297:CHECK_FAIL_RETURN_STATUS(connectTimeoutMs_ &gt;= 0, K_INVALID, "The connection timeout must be a positive integer."); | 298:HeartbeatType heartbeatType = enableHeartbeat ? HeartbeatType::RPC_HEARTBEAT : HeartbeatType::NO_HEARTBEAT;</t>
+- 代码证据: object_client_impl.cpp:329 328:{ | 329:CHECK_FAIL_RETURN_STATUS(connectTimeoutMs_ &gt;= 0, K_INVALID, "The connection timeout must be a positive integer."); | 330:HeartbeatType heartbeatType = enableHeartbeat ? HeartbeatType::RPC_HEARTBEAT : HeartbeatType::NO_HEARTBEAT;</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
         <is>
           <t>返回: Status返回；重试: 通常不重试。
 - 代码锚点: client_worker_common_api.cpp Connect
-- 代码证据: client_worker_common_api.cpp:191 190:Status status; | 191:RETURN_IF_NOT_OK_PRINT_ERROR_MSG(api_-&gt;WorkerRegisterClient(workerService_, req, rsp), "Register client failed"); | 192:VLOG(1) &lt;&lt; "Register response: " &lt;&lt; rsp.DebugString();</t>
+- 代码证据: client_worker_common_api.cpp:217 216:Status status; | 217:RETURN_IF_NOT_OK_PRINT_ERROR_MSG(api_-&gt;WorkerRegisterClient(workerService_, req, rsp), "Register client failed"); | 218:VLOG(1) &lt;&lt; "Register response: " &lt;&lt; rsp.DebugString();</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
         <is>
           <t>返回: 状态直接返回；重试: 连接阶段通常快速失败，业务RPC阶段按 RetryOnError 对 1001/1002/19 退避重试。
 - 代码锚点: client_worker_common_api.cpp; client_worker_remote_api.cpp
-- 代码证据: client_worker_common_api.cpp:136 136:RETURN_STATUS(K_RUNTIME_ERROR, "Not support GetClientFd in embedded scenario");</t>
+- 代码证据: client_worker_common_api.cpp:162 162:RETURN_STATUS(K_RUNTIME_ERROR, "Not support GetClientFd in embedded scenario");</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         <is>
           <t>返回: LOG_IF_ERROR不阻断Init；重试: 通常不重试。
 - 代码锚点: urma_manager.cpp UrmaInit
-- 代码证据: urma_manager.cpp:270 269:if (ret != URMA_SUCCESS) { | 270:RETURN_STATUS_LOG_ERROR(K_URMA_ERROR, FormatString("Failed to urma init, ret = %d", ret)); | 271:}</t>
+- 代码证据: urma_manager.cpp:348 347:if (ret != URMA_SUCCESS) { | 348:RETURN_STATUS_LOG_ERROR(K_URMA_ERROR, FormatString("Failed to urma init, ret = %d", ret)); | 349:}</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
         <is>
           <t>返回: 链上RETURN；重试: 通常不重试。
 - 代码锚点: urma_manager.cpp InitMemoryBufferPool
-- 代码证据: urma_manager.cpp:201 200:if (memoryBuffer_ == nullptr) { | 201:RETURN_STATUS(K_OUT_OF_MEMORY, "Failed to allocate memory buffer pool for client"); | 202:}</t>
+- 代码证据: urma_manager.cpp:265 264:if (memoryBuffer_ == MAP_FAILED) { | 265:RETURN_STATUS(K_OUT_OF_MEMORY, "Failed to allocate memory buffer pool for client"); | 266:}</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         <is>
           <t>返回: 仅ERROR日志；重试: 通常不重试。
 - 代码锚点: urma_manager.cpp ExchangeJfr
-- 代码证据: urma_manager.cpp:63 63:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
+- 代码证据: urma_manager.cpp:96 96:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         <is>
           <t>返回: 直接RETURN；重试: 通常不重试。
 - 代码锚点: client_worker_base_api.cpp PreGet
-- 代码证据: client_worker_base_api.cpp:39 39:LOG(INFO) &lt;&lt; FormatString("Begin to publish object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
+- 代码证据: client_worker_base_api.cpp:33 33:static constexpr int DEBUG_LOG_LEVEL = 2;</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
         <is>
           <t>返回: 不返回URMA码继续RPC；重试: 通常不重试。
 - 代码锚点: client_worker_base_api.cpp PrepareUrmaBuffer
-- 代码证据: client_worker_base_api.cpp:82 81:if (ubRc.IsError()) { | 82:LOG(WARNING) &lt;&lt; "Prepare UB Get request failed: " &lt;&lt; ubRc.ToString() &lt;&lt; ", fallback to TCP/IP payload."; | 83:ubBufferHandle.reset();</t>
+- 代码证据: client_worker_base_api.cpp:117 116:LOG(WARNING) &lt;&lt; "UB Get buffer size " &lt;&lt; requiredSize &lt;&lt; " exceeds max " &lt;&lt; maxGetSize | 117:&lt;&lt; ", fallback to TCP/IP payload."; | 118:return;</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
         <is>
           <t>返回: Status返回；重试: RetryOnError。
 - 代码锚点: client_worker_remote_api.cpp Get
-- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
+- 代码证据: client_worker_remote_api.cpp:134 134:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
         <is>
           <t>返回: 重试后返回；重试: RetryOnError。
 - 代码锚点: client_worker_remote_api.cpp
-- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
+- 代码证据: client_worker_remote_api.cpp:134 134:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         <is>
           <t>返回: 重试；重试: 见RPC。
 - 代码锚点: client_worker_remote_api.cpp Get lambda
-- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
+- 代码证据: client_worker_remote_api.cpp:134 134:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
         <is>
           <t>返回: last_rc；重试: worker内策略。
 - 代码锚点: worker_oc_service_get_impl.cpp
-- 代码证据: worker_oc_service_get_impl.cpp:1583 1582:auto metaPb = std::make_unique&lt;ObjectMetaPb&gt;(); | 1583:CHECK_FAIL_RETURN_STATUS(!etcdStore_-&gt;IsKeepAliveTimeout(), K_RPC_UNAVAILABLE, "etcd is unavailable"); | 1584:RangeSearchResult res;</t>
+- 代码证据: worker_oc_service_get_impl.cpp:1615 1614:auto metaPb = std::make_unique&lt;ObjectMetaPb&gt;(); | 1615:CHECK_FAIL_RETURN_STATUS(!etcdStore_-&gt;IsKeepAliveTimeout(), K_RPC_UNAVAILABLE, "etcd is unavailable"); | 1616:RangeSearchResult res;</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
         <is>
           <t>返回: last_rc；重试: 视实现。
 - 代码锚点: worker_oc_service_get_impl.cpp
-- 代码证据: worker_oc_service_get_impl.cpp:700 699:} | 700:RETURN_STATUS_LOG_ERROR(K_RUNTIME_ERROR, FormatString("Query from master failed : %s", result.ToString())); | 701:}</t>
+- 代码证据: worker_oc_service_get_impl.cpp:716 715:} | 716:RETURN_STATUS_LOG_ERROR(K_RUNTIME_ERROR, FormatString("Query from master failed : %s", result.ToString())); | 717:}</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
         <is>
           <t>返回: last_rc/RPC；重试: TryReconnect…。
 - 代码锚点: worker_oc_service_get_impl.cpp
-- 代码证据: worker_oc_service_get_impl.cpp:1733 1732:} else { | 1733:LOG(ERROR) &lt;&lt; FormatString("[ObjectKey %s] Get from remote failed: %s.", objectKey, status.ToString()); | 1734:failedIds.emplace(objectKey);</t>
+- 代码证据: worker_oc_service_get_impl.cpp:1766 1765:} else { | 1766:LOG(ERROR) &lt;&lt; FormatString("[ObjectKey %s] Get from remote failed: %s.", objectKey, status.ToString()); | 1767:lastRc = status;</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
         <is>
           <t>返回: 汇总回 client；重试: 通常不重试。
 - 代码锚点: urma_manager.cpp
-- 代码证据: urma_manager.cpp:63 63:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
+- 代码证据: urma_manager.cpp:96 96:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
         <is>
           <t>返回: 汇总回 client；重试: 通常不重试。
 - 代码锚点: urma_manager.cpp PollJfcWait
-- 代码证据: urma_manager.cpp:63 63:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
+- 代码证据: urma_manager.cpp:96 96:VLOG(RPC_LOG_LEVEL) &lt;&lt; "UrmaManager::UrmaManager()";</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
         <is>
           <t>返回: Status；重试: 通常不重试。
 - 代码锚点: urma_manager.cpp
-- 代码证据: urma_manager.cpp:1263 1262:} | 1263:RETURN_STATUS(K_URMA_NEED_CONNECT, "Urma connect unstable, need to reconnect!"); | 1264:}</t>
+- 代码证据: urma_manager.cpp:1308 1307:} | 1308:RETURN_STATUS(K_URMA_NEED_CONNECT, "Urma connect unstable, need to reconnect!"); | 1309:}</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
         <is>
           <t>返回: 直接RETURN；重试: 通常不重试。
 - 代码锚点: client_worker_base_api.cpp FillUrmaBuffer
-- 代码证据: client_worker_base_api.cpp:107 106:ubReadOffset &lt;= ubBufferSize &amp;&amp; payloadSize &lt;= ubBufferSize - ubReadOffset, K_RUNTIME_ERROR, | 107:FormatString("UB payload overflow, object %s, payload size %llu, consumed %llu, buffer size %llu", | 108:payloadInfo-&gt;object_key(), payloadSize, ubReadOffset, ubBufferSize));</t>
+- 代码证据: client_worker_base_api.cpp:156 155:ubReadOffset &lt;= ubBufferSize &amp;&amp; payloadSize &lt;= ubBufferSize - ubReadOffset, K_RUNTIME_ERROR, | 156:FormatString("UB payload overflow, object %s, payload size %llu, consumed %llu, buffer size %llu", | 157:payloadInfo-&gt;object_key(), payloadSize, ubReadOffset, ubBufferSize));</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
         <is>
           <t>返回: 单key失败聚合；重试: 通常不重试。
 - 代码锚点: object_client_impl.cpp MmapShmUnit
-- 代码证据: object_client_impl.cpp:1112 1111:mmapEntry = mmapManager_-&gt;GetMmapEntryByFd(shmBuf-&gt;fd); | 1112:CHECK_FAIL_RETURN_STATUS(mmapEntry != nullptr, StatusCode::K_RUNTIME_ERROR, "Get mmap entry failed"); | 1113:bufferInfo =</t>
+- 代码证据: object_client_impl.cpp:1296 1295:mmapEntry = mmapManager_-&gt;GetMmapEntryByFd(shmBuf-&gt;fd); | 1296:CHECK_FAIL_RETURN_STATUS(mmapEntry != nullptr, StatusCode::K_RUNTIME_ERROR, "Get mmap entry failed"); | 1297:bufferInfo =</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
         <is>
           <t>返回: last_rc；重试: 通常不重试。
 - 代码锚点: worker_oc_service_get_impl.cpp
-- 代码证据: worker_oc_service_get_impl.cpp:250 249:(void)RemoveLocation(objectKey, version); | 250:return Status(StatusCode::K_NOT_FOUND, "Object not found"); | 251:}</t>
+- 代码证据: worker_oc_service_get_impl.cpp:252 251:(void)RemoveLocation(objectKey, version); | 252:return Status(StatusCode::K_NOT_FOUND, "Object not found"); | 253:}</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
         <is>
           <t>返回: 可改走非UB；重试: 通常不重试。
 - 代码锚点: client_worker_base_api.cpp SendBufferViaUb
-- 代码证据: client_worker_base_api.cpp:146 145:#endif | 146:return Status(K_INVALID, "Failed to send buffer via UB"); | 147:}</t>
+- 代码证据: client_worker_base_api.cpp:279 278:#else | 279:return Status(K_INVALID, "Failed to send buffer via UB"); | 280:#endif</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
         <is>
           <t>返回: Status；重试: RetryOnError。
 - 代码锚点: client_worker_remote_api.cpp Publish
-- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
+- 代码证据: client_worker_remote_api.cpp:134 134:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         <is>
           <t>返回: 重试后返回；重试: RetryOnError。
 - 代码锚点: client_worker_remote_api.cpp
-- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
+- 代码证据: client_worker_remote_api.cpp:134 134:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
         <is>
           <t>返回: Status；重试: RetryOnError含扩展码。
 - 代码锚点: client_worker_remote_api.cpp MultiPublish
-- 代码证据: client_worker_remote_api.cpp:115 115:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
+- 代码证据: client_worker_remote_api.cpp:134 134:LOG(INFO) &lt;&lt; FormatString("Begin to create object, client id: %s, worker address: %s, object key: %s", clientId_,</t>
         </is>
       </c>
     </row>
@@ -2205,19 +2205,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2228,47 +2224,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>调用链(树状)</t>
+          <t>对应接口(Init/Get/Set)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>责任归属</t>
+          <t>关键日志(检测用)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>包装符号/文件</t>
+          <t>映射关系(数据系统错误码)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>所在链路</t>
+          <t>错误码(分行+含义)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>典型失败case</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>OS原生错误码(errno/zmq)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>系统映射码(Status)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>日志关键词</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>定位建议(简短)</t>
+          <t>可能原因与应对</t>
         </is>
       </c>
     </row>
@@ -2280,95 +2256,68 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>InitClientWorkerConnect
-  |_ Connect</t>
+          <t>Init</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>OS</t>
+          <t>Register client failed
+rpc unavailable</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Connect</t>
+          <t>ETIMEDOUT/ECONNREFUSED -&gt; K_RPC_DEADLINE_EXCEEDED(1001)/K_RPC_UNAVAILABLE(1002)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>client1-&gt;worker1 控制面RPC</t>
+          <t>ETIMEDOUT(110): 连接超时
+ECONNREFUSED(111): 对端拒绝
+ENETUNREACH(101): 网络不可达</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ECONNREFUSED/ENETUNREACH/ETIMEDOUT</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1002/1001</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Register client failed</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>查端口、路由、worker 存活</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n"/>
+          <t>可能: worker未监听/网络路由异常；应对: 查端口、防火墙、路由、worker存活</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>send/recv</t>
+          <t>send/recv (含 zmq_send/zmq_recv)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>stub_-&gt;Get/Publish
-  |_ 底层socket读写</t>
+          <t>Get/Set</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>OS+RPC框架</t>
+          <t>rpc unavailable
+try again
+send/recv failed</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ZMQ/TCP socket 层</t>
+          <t>EPIPE/ECONNRESET/EAGAIN -&gt; K_RPC_UNAVAILABLE(1002)/K_TRY_AGAIN(19)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>client1-&gt;worker1 控制面RPC</t>
+          <t>EPIPE(32): 连接已断开
+ECONNRESET(104): 对端重置
+EAGAIN(11): 资源暂不可用</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>EPIPE/ECONNRESET/EAGAIN</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1002/19</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>rpc unavailable/try again</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>查网络抖动、连接复用、对端重启</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n"/>
+          <t>可能: 网络抖动/对端重启/连接复用异常；应对: 对齐client-worker同key时间线并抓包</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2378,388 +2327,101 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>stub_-&gt;Get/Publish
-  |_ zmq_poll</t>
+          <t>Init/Get/Set</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>OS+RPC框架</t>
+          <t>rpc timeout
+time elapsed</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ZMQ poll</t>
+          <t>ETIMEDOUT -&gt; K_RPC_DEADLINE_EXCEEDED(1001)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>client1-&gt;worker1 控制面RPC</t>
+          <t>ETIMEDOUT(110): 等待超时</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ETIMEDOUT</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>rpc timeout / time elapsed</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>查超时配置、队列堆积、线程池阻塞</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n"/>
+          <t>可能: 队列堆积/线程池阻塞/超时配置过小；应对: 查超时参数和worker负载</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>sendmsg</t>
+          <t>sendmsg/recvmsg (UDS传fd)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PostRegisterClient
-  |_ SockSendFd</t>
+          <t>Init</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>OS</t>
+          <t>Pass fd meets unexpected error
+Unexpected EOF read
+invalid fd</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>SockSendFd</t>
+          <t>EBADF/EOF -&gt; K_UNKNOWN_ERROR 或 K_RUNTIME_ERROR(5)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>UDS 传 fd</t>
+          <t>EBADF(9): 非法文件描述符
+EINTR(4): 调用被中断
+EOF: 对端提前关闭</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>EAGAIN/EINTR/其他errno</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>K_UNKNOWN_ERROR</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Pass fd meets unexpected error</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>查对端是否收、socket是否断开</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n"/>
+          <t>可能: fd传递时序异常/对端提前退出；应对: 联查SockSendFd/SockRecvFd配对日志</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>recvmsg</t>
+          <t>mmap (anon/file)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PostRegisterClient
-  |_ SockRecvFd</t>
+          <t>Init/Get</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>OS</t>
+          <t>Failed to allocate memory buffer pool
+Get mmap entry failed</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SemiSockRecvFd</t>
+          <t>ENOMEM/EBADF/EACCES -&gt; K_OUT_OF_MEMORY(6)/K_RUNTIME_ERROR(5)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>UDS 收 fd</t>
+          <t>ENOMEM(12): 内存不足
+EBADF(9): fd无效
+EACCES(13): 权限不足</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>EOF/EBADF</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>K_UNKNOWN_ERROR</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Unexpected EOF read / invalid fd</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>查 worker 是否提前关连接或先发后断</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>GetClientFd
-  |_ close</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>OS</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>RETRY_ON_EINTR(close)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>fd 清理</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>EBADF/EINTR</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>多为LOG</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Close expired fds / errno</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>查 fd 泄漏与 ulimit -n</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>mmap(anon)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>InitMemoryBufferPool
-  |_ mmap</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>OS</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>InitMemoryBufferPool</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>UB 客户端池</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>ENOMEM</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>K_OUT_OF_MEMORY(6)</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Failed to allocate memory buffer pool</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>查内存与 vm.max_map_count</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>mmap(file)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>MmapShmUnit
-  |_ LookupUnitsAndMmapFd</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>OS+数据系统</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>MmapManager::LookupUnitsAndMmapFd</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>SHM 读路径⑥</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>EBADF/ENOMEM/EACCES</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>K_RUNTIME_ERROR(5)</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Get mmap entry failed</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>查 store_fd 是否与 RecvPageFd 对齐</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>munmap</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>~UrmaManager</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>OS</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>~UrmaManager</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>进程退出</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>EINVAL</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>LOG</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>UrmaManager destructor</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>一般排障可忽略除非崩溃链</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>usleep</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>PollJfcWait
-  |_ usleep</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>OS</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>PollJfcWait 轮询路径</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>URMA 等待</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>多为延迟非错误</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Failed to poll jfc</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>性能问题看 Sheet4 与 CPU</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n"/>
+          <t>可能: 内存上限/fd异常/权限问题；应对: 查ulimit、vm.max_map_count、fd来源</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2772,70 +2434,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>URMA C接口</t>
+          <t>URMA接口</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>调用链(树状)</t>
+          <t>对应接口(Init/Get/Set)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>责任归属</t>
+          <t>关键日志(检测用)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>调用模块/符号</t>
+          <t>映射关系(数据系统错误码)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>所在流程</t>
+          <t>错误码(分行+含义)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>典型失败case</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>URMA原生状态码</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>系统映射码(Status)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>日志关键词</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>定位建议(简短)</t>
+          <t>可能原因与应对</t>
         </is>
       </c>
     </row>
@@ -2847,681 +2485,207 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PostRegisterClient
-  |_ FastTransportHandshake
-    |_ UrmaInit</t>
+          <t>Init</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>Failed to urma init, ret = %d
+Failed to urma uninit, ret = %d</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>UrmaInit / UrmaUninit</t>
+          <t>ret != URMA_SUCCESS -&gt; K_URMA_ERROR(1004)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Init</t>
+          <t>URMA_EINVAL(22): 参数非法
+URMA_EEXIST(17): 重复初始化
+URMA_FAIL(0x1000): 通用失败</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>URMA_SUCCESS / 非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>K_URMA_ERROR(1004)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Failed to urma init/uninit</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>查 UMDK 安装与内核/驱动</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n"/>
+          <t>可能: UMDK/驱动/设备配置异常；应对: 查设备、驱动、UMDK部署与权限</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>urma_register_log_func</t>
+          <t>urma_get_device_by_name / urma_get_eid_list / urma_query_device</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>UrmaInit
-  |_ RegisterUrmaLog</t>
+          <t>Init</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>Failed to urma get device by name, errno = %d
+Failed to urma get eid list, errno = %d</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>RegisterUrmaLog</t>
+          <t>接口失败 -&gt; K_URMA_ERROR(1004) 或 K_RUNTIME_ERROR(5)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Init</t>
+          <t>URMA_EINVAL(22): 参数非法
+URMA_ENOMEM(12): 内存不足
+URMA_FAIL(0x1000): 设备查询失败</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>URMA_SUCCESS / 非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Failed to urma register log</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>不影响主链可先忽略或查权限</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n"/>
+          <t>可能: 设备名不匹配/EID配置异常；应对: 核对 DS_URMA_DEV_NAME、bonding、EID</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>urma_get_device_list / urma_get_device_by_name</t>
+          <t>urma_create_* / urma_import_jfr / urma_advise_jfr</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>UrmaGetEffectiveDevice</t>
+          <t>Init/Get/Set</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>Failed to urma create ...
+Failed to import target jfr
+Failed to advise jfr</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>UrmaGetEffectiveDevice</t>
+          <t>创建/导入失败 -&gt; K_URMA_ERROR(1004) 或 K_RUNTIME_ERROR(5)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Init</t>
+          <t>URMA_ENOPERM(1): 模式或权限不允许
+URMA_EINPROGRESS(115): 连接处理中
+URMA_FAIL(0x1000): 导入失败</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>返回NULL或设备不匹配</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>K_RUNTIME_ERROR/1004</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>bonding device / errno</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>核对 DS_URMA_DEV_NAME 与 bonding</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n"/>
+          <t>可能: 资源上限/握手时序/对端jfr状态异常；应对: 查连接重建与两端握手日志</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>urma_query_device / urma_get_eid_list</t>
+          <t>urma_write / urma_read / urma_post_jfs_wr</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UrmaGetEffectiveDevice
-  |_ UrmaQueryDevice</t>
+          <t>Get/Set</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>Failed to urma write object ...
+Failed to urma read object ...</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>UrmaQueryDevice</t>
+          <t>数据面失败 -&gt; K_URMA_ERROR(1004) 或 K_RUNTIME_ERROR(5)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Init</t>
+          <t>URMA_ETIMEOUT(110): 操作超时
+URMA_EAGAIN(11): 资源暂不可用
+URMA_ENOMEM(12): 资源不足</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Failed to urma query/get eid</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>查设备能力与 EID 配置</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n"/>
+          <t>可能: 链路抖动/远端状态异常/CQ积压；应对: 结合 CR.status 与 jfc 轮询日志</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>urma_create_context</t>
+          <t>urma_wait_jfc / urma_poll_jfc / urma_rearm_jfc</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>UrmaInit
-  |_ UrmaCreateContext</t>
+          <t>Get/Set</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>Failed to wait jfc, ret = %d
+Failed to poll jfc, ret = %d
+Failed to rearm jfc, status = %d</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>UrmaCreateContext</t>
+          <t>轮询失败 -&gt; K_URMA_ERROR(1004)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Init</t>
+          <t>URMA_CR_ACK_TIMEOUT_ERR(9): ACK超时
+URMA_CR_REM_ACCESS_ABORT_ERR(8): 远端访问中止
+URMA_CR_RNR_RETRY_CNT_EXC_ERR(10): RNR重试超限</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>context为空</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Failed to urma create context</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>查资源配额与设备占用</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
+          <t>可能: CQ事件流转异常/对端无buffer/链路不稳；应对: 优先看 CR.status，再看重建JFS是否触发</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>urma_create_jfc/jfs/jfr/jfce</t>
+          <t>CheckUrmaConnectionStable(逻辑)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UrmaInit
-  |_ UrmaCreate*</t>
+          <t>Get/Set</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>No existing connection requires creation.
+Urma connect unstable, need to reconnect!</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>UrmaCreate*</t>
+          <t>连接不稳定 -&gt; K_URMA_NEED_CONNECT(1006)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Init</t>
+          <t>K_URMA_NEED_CONNECT(1006): 需要重连（非OS connect错误）</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>创建返回失败</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Failed to urma create jfc/jfs/jfr</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>查 UMDK 资源上限</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>urma_register_seg</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>InitMemoryBufferPool
-  |_ Segment::Set</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>URMA</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>InitMemoryBufferPool</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Init</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>register seg</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>查 mmap 后注册是否成功</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>urma_import_jfr / urma_advise_jfr</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>ExchangeJfr
-  |_ ImportRemoteJfr</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>URMA</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ImportRemoteJfr / ExchangeJfr</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>握手</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1004/K_RUNTIME_ERROR</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Failed to import/advise jfr</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>查对端 jfr 与网络时序</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>urma_import_seg / urma_unimport_seg</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>ImportSegment
-  |_ Segment::Set</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>URMA</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>ImportSegment / Segment::Set</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>数据面</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>K_RUNTIME_ERROR</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>segment</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>查 seg_va 与对端是否一致</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>urma_write / urma_read</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>UrmaWritePayload
-  |_ UrmaWrite/UrmaRead</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>URMA</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>UrmaWrite / UrmaRead</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>读写数据面</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>K_RUNTIME_ERROR(5)</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Failed to urma write/read</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>查对端与链路；读完成错误看 CR.status</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>urma_post_jfs_wr</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Post...Wr</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>URMA</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Post...Wr</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>批量写</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>non-success + bad_wr</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>K_RUNTIME_ERROR</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Failed to urma write object</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>查 sge 与 remote jfr</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>urma_wait_jfc / urma_poll_jfc</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>PollJfcWait
-  |_ urma_wait/poll_jfc</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>URMA</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>PollJfcWait</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>完成队列</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>cnt&lt;0 / 非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Failed to wait/poll jfc</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>查设备/CQ/事件模式配置</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>urma_ack_jfc / urma_rearm_jfc</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>PollJfcWait
-  |_ urma_ack/rearm_jfc</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>URMA</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>PollJfcWait</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>事件模式</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>非URMA_SUCCESS</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Failed to rearm jfc</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>查 jfc 事件线程与状态机</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>(无直接 urma_* 调用)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>CheckUrmaConnectionStable</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>数据系统逻辑</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>CheckUrmaConnectionStable</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>读写前</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>连接计数/instance 逻辑判定</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>need to reconnect</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>按提示触发重连/重建会话</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n"/>
+          <t>可能: 连接已失效或实例ID不一致；应对: 触发重建UB会话并重试</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
